--- a/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0001T0006Z000C1N10_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0001T0006Z000C1N10_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>17.35213001637113</v>
+        <v>2.819721127660309</v>
       </c>
       <c r="D2" t="n">
-        <v>17.04673502285799</v>
+        <v>2.770094441214423</v>
       </c>
       <c r="E2" t="n">
-        <v>17.88202874438406</v>
+        <v>2.90582967096241</v>
       </c>
       <c r="F2" t="n">
-        <v>16.07372528323675</v>
+        <v>2.611980358525972</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>40.2293526949975</v>
+        <v>6.537269812937094</v>
       </c>
       <c r="D3" t="n">
-        <v>40.1461148709153</v>
+        <v>6.523743666523736</v>
       </c>
       <c r="E3" t="n">
-        <v>17.88202874438406</v>
+        <v>2.90582967096241</v>
       </c>
       <c r="F3" t="n">
-        <v>16.07372528323675</v>
+        <v>2.611980358525972</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>62.11898799208853</v>
+        <v>10.09433554871439</v>
       </c>
       <c r="D4" t="n">
-        <v>62.33423344009896</v>
+        <v>10.12931293401608</v>
       </c>
       <c r="E4" t="n">
-        <v>17.88202874438406</v>
+        <v>2.90582967096241</v>
       </c>
       <c r="F4" t="n">
-        <v>16.07372528323675</v>
+        <v>2.611980358525972</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>20.68663850932363</v>
+        <v>3.361578757765089</v>
       </c>
       <c r="D5" t="n">
-        <v>36.60890641425714</v>
+        <v>5.948947292316785</v>
       </c>
       <c r="E5" t="n">
-        <v>17.88202874438406</v>
+        <v>2.90582967096241</v>
       </c>
       <c r="F5" t="n">
-        <v>16.07372528323675</v>
+        <v>2.611980358525972</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
